--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.59096546743924</v>
+        <v>7.896031888458877</v>
       </c>
       <c r="D2" t="n">
-        <v>48.18925440522982</v>
+        <v>7.830753840849847</v>
       </c>
       <c r="E2" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F2" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67509049579485</v>
+        <v>5.634702205566663</v>
       </c>
       <c r="D3" t="n">
-        <v>34.64876517647202</v>
+        <v>5.630424341176703</v>
       </c>
       <c r="E3" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F3" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.45496899395542</v>
+        <v>6.086432461517756</v>
       </c>
       <c r="D4" t="n">
-        <v>36.50773218776714</v>
+        <v>5.932506480512161</v>
       </c>
       <c r="E4" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F4" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.82970856056874</v>
+        <v>7.284827641092421</v>
       </c>
       <c r="D5" t="n">
-        <v>44.7722028303093</v>
+        <v>7.275482959925262</v>
       </c>
       <c r="E5" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F5" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.81102623982111</v>
+        <v>4.03179176397093</v>
       </c>
       <c r="D6" t="n">
-        <v>9.227906677217705</v>
+        <v>1.499534835047877</v>
       </c>
       <c r="E6" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F6" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.46067079082782</v>
+        <v>4.29985900350952</v>
       </c>
       <c r="D7" t="n">
-        <v>27.22668668932908</v>
+        <v>4.424336587015976</v>
       </c>
       <c r="E7" t="n">
-        <v>8.722076283778533</v>
+        <v>1.417337396114012</v>
       </c>
       <c r="F7" t="n">
-        <v>12.79102150987633</v>
+        <v>2.078540995354904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
